--- a/5/search/FY4_Missile2_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY4_Missile2_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>292</v>
+        <v>295.4</v>
       </c>
       <c r="C3" t="n">
-        <v>122.7</v>
+        <v>105.8</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>3.599999999999998</v>
+        <v>3.699999999999999</v>
       </c>
     </row>
   </sheetData>
